--- a/public/market_data.xlsx
+++ b/public/market_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ismae\Documents\GitHub\galetaireID\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792500BF-5DE1-4D04-8090-BD00BA187950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7844D2-5B41-4481-9762-CD2E0B90F597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{CD70AFFB-D9AB-4B42-B823-CE9D5850E5EA}"/>
   </bookViews>
@@ -778,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B6E76A0-00D2-4583-AD01-5FF02B5D1606}">
-  <dimension ref="A1:AP37"/>
+  <dimension ref="A1:AP38"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.54296875" customWidth="1"/>
@@ -982,7 +982,7 @@
       </c>
       <c r="O2" s="20">
         <f t="shared" ref="O2:O37" si="2">J2*MAX($D$2:$D$37)/MAX($J$2:$J$37)</f>
-        <v>0.99464656002974439</v>
+        <v>1.0023917061605945</v>
       </c>
       <c r="P2" s="5">
         <f t="shared" ref="P2:P37" si="3">L2*MAX($D$2:$D$37)/MAX($L$2:$L$37)</f>
@@ -990,11 +990,11 @@
       </c>
       <c r="Q2" s="7">
         <f t="shared" ref="Q2:Q37" si="4">(F2*100/MAX($F$2:$F$37))</f>
-        <v>4.2358452241913369</v>
+        <v>4.2518763937559738</v>
       </c>
       <c r="R2" s="7">
         <f t="shared" ref="R2:R37" si="5">(H2*MAX($Q$2:$Q$37)/MAX($H$2:$H$37))</f>
-        <v>14.728518949914879</v>
+        <v>14.670028111195391</v>
       </c>
       <c r="S2" s="36"/>
       <c r="T2" s="35">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O3" s="20">
         <f t="shared" si="2"/>
-        <v>1.209218419874007</v>
+        <v>1.2186344011304644</v>
       </c>
       <c r="P3" s="5">
         <f t="shared" si="3"/>
@@ -1133,11 +1133,11 @@
       </c>
       <c r="Q3" s="7">
         <f t="shared" si="4"/>
-        <v>5.2960823642918804</v>
+        <v>5.3161261548263781</v>
       </c>
       <c r="R3" s="7">
         <f t="shared" si="5"/>
-        <v>15.147388226861391</v>
+        <v>15.087233947615006</v>
       </c>
       <c r="S3" s="36">
         <f>E3-E2</f>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="O4" s="20">
         <f t="shared" si="2"/>
-        <v>1.2646884143320229</v>
+        <v>1.2745363311424946</v>
       </c>
       <c r="P4" s="5">
         <f t="shared" si="3"/>
@@ -1287,11 +1287,11 @@
       </c>
       <c r="Q4" s="7">
         <f t="shared" si="4"/>
-        <v>5.6011146092520203</v>
+        <v>5.6223128384835954</v>
       </c>
       <c r="R4" s="7">
         <f t="shared" si="5"/>
-        <v>15.31717588029746</v>
+        <v>15.256347329436432</v>
       </c>
       <c r="S4" s="36">
         <f>E4-(AVERAGE(E2:E3))</f>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="O5" s="20">
         <f t="shared" si="2"/>
-        <v>1.4090842275972424</v>
+        <v>1.4200565304151302</v>
       </c>
       <c r="P5" s="5">
         <f t="shared" si="3"/>
@@ -1441,11 +1441,11 @@
       </c>
       <c r="Q5" s="7">
         <f t="shared" si="4"/>
-        <v>6.3424694053724684</v>
+        <v>6.3664733991717117</v>
       </c>
       <c r="R5" s="7">
         <f t="shared" si="5"/>
-        <v>15.567153480870887</v>
+        <v>15.505332202936055</v>
       </c>
       <c r="S5" s="36">
         <f t="shared" ref="S5:S37" si="22">E5-(AVERAGE(E3:E4))</f>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="O6" s="20">
         <f t="shared" si="2"/>
-        <v>1.4155916518517733</v>
+        <v>1.4266146268921491</v>
       </c>
       <c r="P6" s="5">
         <f t="shared" si="3"/>
@@ -1595,11 +1595,11 @@
       </c>
       <c r="Q6" s="7">
         <f t="shared" si="4"/>
-        <v>6.4038490834306616</v>
+        <v>6.4280853775087623</v>
       </c>
       <c r="R6" s="7">
         <f t="shared" si="5"/>
-        <v>15.645551473882268</v>
+        <v>15.583418856811385</v>
       </c>
       <c r="S6" s="36">
         <f t="shared" si="22"/>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="O7" s="20">
         <f t="shared" si="2"/>
-        <v>1.8226345912694426</v>
+        <v>1.8368271414875845</v>
       </c>
       <c r="P7" s="5">
         <f t="shared" si="3"/>
@@ -1749,11 +1749,11 @@
       </c>
       <c r="Q7" s="7">
         <f t="shared" si="4"/>
-        <v>8.6123495658355775</v>
+        <v>8.6449442497610711</v>
       </c>
       <c r="R7" s="7">
         <f t="shared" si="5"/>
-        <v>16.342173640354805</v>
+        <v>16.277274552675024</v>
       </c>
       <c r="S7" s="36">
         <f t="shared" si="22"/>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="O8" s="20">
         <f t="shared" si="2"/>
-        <v>2.1728085188826585</v>
+        <v>2.1897278148108517</v>
       </c>
       <c r="P8" s="5">
         <f t="shared" si="3"/>
@@ -1903,11 +1903,11 @@
       </c>
       <c r="Q8" s="7">
         <f t="shared" si="4"/>
-        <v>10.764319809069214</v>
+        <v>10.805058935966871</v>
       </c>
       <c r="R8" s="7">
         <f t="shared" si="5"/>
-        <v>17.133769375503984</v>
+        <v>17.065726652090486</v>
       </c>
       <c r="S8" s="36">
         <f t="shared" si="22"/>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="O9" s="20">
         <f t="shared" si="2"/>
-        <v>2.5308012091505976</v>
+        <v>2.5505081341837648</v>
       </c>
       <c r="P9" s="5">
         <f t="shared" si="3"/>
@@ -2057,11 +2057,11 @@
       </c>
       <c r="Q9" s="7">
         <f t="shared" si="4"/>
-        <v>13.263977047681916</v>
+        <v>13.31417648932781</v>
       </c>
       <c r="R9" s="7">
         <f t="shared" si="5"/>
-        <v>18.126063972762296</v>
+        <v>18.054080585426796</v>
       </c>
       <c r="S9" s="36">
         <f t="shared" si="22"/>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="O10" s="20">
         <f t="shared" si="2"/>
-        <v>2.8119100408853717</v>
+        <v>2.8338059132973878</v>
       </c>
       <c r="P10" s="5">
         <f t="shared" si="3"/>
@@ -2211,11 +2211,11 @@
       </c>
       <c r="Q10" s="7">
         <f t="shared" si="4"/>
-        <v>15.998616259584628</v>
+        <v>16.059165339280028</v>
       </c>
       <c r="R10" s="7">
         <f t="shared" si="5"/>
-        <v>19.67744825732461</v>
+        <v>19.599303913256875</v>
       </c>
       <c r="S10" s="36">
         <f t="shared" si="22"/>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="O11" s="20">
         <f t="shared" si="2"/>
-        <v>2.9544738740205583</v>
+        <v>2.9774798671176277</v>
       </c>
       <c r="P11" s="5">
         <f t="shared" si="3"/>
@@ -2365,11 +2365,11 @@
       </c>
       <c r="Q11" s="7">
         <f t="shared" si="4"/>
-        <v>17.81739704463515</v>
+        <v>17.884829563555275</v>
       </c>
       <c r="R11" s="7">
         <f t="shared" si="5"/>
-        <v>20.857002060747242</v>
+        <v>20.774173396992541</v>
       </c>
       <c r="S11" s="36">
         <f t="shared" si="22"/>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="O12" s="20">
         <f t="shared" si="2"/>
-        <v>2.8779857608491688</v>
+        <v>2.9003961538229466</v>
       </c>
       <c r="P12" s="5">
         <f t="shared" si="3"/>
@@ -2519,11 +2519,11 @@
       </c>
       <c r="Q12" s="7">
         <f t="shared" si="4"/>
-        <v>18.50656324582339</v>
+        <v>18.576604014017203</v>
       </c>
       <c r="R12" s="7">
         <f t="shared" si="5"/>
-        <v>22.239494668936477</v>
+        <v>22.151175761902635</v>
       </c>
       <c r="S12" s="36">
         <f t="shared" si="22"/>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="O13" s="20">
         <f t="shared" si="2"/>
-        <v>2.3627081273767172</v>
+        <v>2.3811061397425699</v>
       </c>
       <c r="P13" s="5">
         <f t="shared" si="3"/>
@@ -2673,11 +2673,11 @@
       </c>
       <c r="Q13" s="7">
         <f t="shared" si="4"/>
-        <v>16.65511857005027</v>
+        <v>16.718152277795475</v>
       </c>
       <c r="R13" s="7">
         <f t="shared" si="5"/>
-        <v>24.37953588388137</v>
+        <v>24.282718307973759</v>
       </c>
       <c r="S13" s="36">
         <f t="shared" si="22"/>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O14" s="20">
         <f t="shared" si="2"/>
-        <v>1.7860027497573963</v>
+        <v>1.7999100539625781</v>
       </c>
       <c r="P14" s="5">
         <f t="shared" si="3"/>
@@ -2827,11 +2827,11 @@
       </c>
       <c r="Q14" s="7">
         <f t="shared" si="4"/>
-        <v>13.40023104656477</v>
+        <v>13.450946161197834</v>
       </c>
       <c r="R14" s="7">
         <f t="shared" si="5"/>
-        <v>25.948839709703428</v>
+        <v>25.845790013832488</v>
       </c>
       <c r="S14" s="36">
         <f t="shared" si="22"/>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="O15" s="20">
         <f t="shared" si="2"/>
-        <v>2.1932907507251507</v>
+        <v>2.2103695383613342</v>
       </c>
       <c r="P15" s="5">
         <f t="shared" si="3"/>
@@ -2981,11 +2981,11 @@
       </c>
       <c r="Q15" s="7">
         <f t="shared" si="4"/>
-        <v>17.224292895952878</v>
+        <v>17.289480726345975</v>
       </c>
       <c r="R15" s="7">
         <f t="shared" si="5"/>
-        <v>27.160200698862106</v>
+        <v>27.052340368568998</v>
       </c>
       <c r="S15" s="36">
         <f t="shared" si="22"/>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="O16" s="20">
         <f t="shared" si="2"/>
-        <v>2.1659538222202008</v>
+        <v>2.1828197417738435</v>
       </c>
       <c r="P16" s="5">
         <f t="shared" si="3"/>
@@ -3135,11 +3135,11 @@
       </c>
       <c r="Q16" s="7">
         <f t="shared" si="4"/>
-        <v>17.987368608134869</v>
+        <v>18.055444409047468</v>
       </c>
       <c r="R16" s="7">
         <f t="shared" si="5"/>
-        <v>28.72144073111728</v>
+        <v>28.607380304314837</v>
       </c>
       <c r="S16" s="36">
         <f t="shared" si="22"/>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="O17" s="20">
         <f t="shared" si="2"/>
-        <v>2.0695661161070023</v>
+        <v>2.085681480740873</v>
       </c>
       <c r="P17" s="5">
         <f t="shared" si="3"/>
@@ -3289,11 +3289,11 @@
       </c>
       <c r="Q17" s="7">
         <f t="shared" si="4"/>
-        <v>17.989260143198091</v>
+        <v>18.057343102899015</v>
       </c>
       <c r="R17" s="7">
         <f t="shared" si="5"/>
-        <v>30.062270405877605</v>
+        <v>29.942885190308321</v>
       </c>
       <c r="S17" s="36">
         <f t="shared" si="22"/>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="O18" s="20">
         <f t="shared" si="2"/>
-        <v>2.2508731504951331</v>
+        <v>2.2684003226316061</v>
       </c>
       <c r="P18" s="5">
         <f t="shared" si="3"/>
@@ -3443,11 +3443,11 @@
       </c>
       <c r="Q18" s="7">
         <f t="shared" si="4"/>
-        <v>20.687744376174276</v>
+        <v>20.766040140172031</v>
       </c>
       <c r="R18" s="7">
         <f t="shared" si="5"/>
-        <v>31.787026252127944</v>
+        <v>31.660791575565568</v>
       </c>
       <c r="S18" s="36">
         <f t="shared" si="22"/>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="O19" s="20">
         <f t="shared" si="2"/>
-        <v>2.2742229351555276</v>
+        <v>2.2919319281533861</v>
       </c>
       <c r="P19" s="5">
         <f t="shared" si="3"/>
@@ -3597,11 +3597,11 @@
       </c>
       <c r="Q19" s="7">
         <f t="shared" si="4"/>
-        <v>22.069796374346215</v>
+        <v>22.153322714240204</v>
       </c>
       <c r="R19" s="7">
         <f t="shared" si="5"/>
-        <v>33.562404802437051</v>
+        <v>33.429119628753725</v>
       </c>
       <c r="S19" s="36">
         <f t="shared" si="22"/>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O20" s="20">
         <f t="shared" si="2"/>
-        <v>1.3351864829388191</v>
+        <v>1.345583356399064</v>
       </c>
       <c r="P20" s="5">
         <f t="shared" si="3"/>
@@ -3751,11 +3751,11 @@
       </c>
       <c r="Q20" s="7">
         <f t="shared" si="4"/>
-        <v>14.289836490123392</v>
+        <v>14.343918445364764</v>
       </c>
       <c r="R20" s="7">
         <f t="shared" si="5"/>
-        <v>37.014604426126681</v>
+        <v>36.867609655972501</v>
       </c>
       <c r="S20" s="36">
         <f t="shared" si="22"/>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="O21" s="20">
         <f t="shared" si="2"/>
-        <v>1.6027710988846779</v>
+        <v>1.6152516089211215</v>
       </c>
       <c r="P21" s="5">
         <f t="shared" si="3"/>
@@ -3905,11 +3905,11 @@
       </c>
       <c r="Q21" s="7">
         <f t="shared" si="4"/>
-        <v>17.534212664398517</v>
+        <v>17.600573431028991</v>
       </c>
       <c r="R21" s="7">
         <f t="shared" si="5"/>
-        <v>37.835767404354449</v>
+        <v>37.685511579135238</v>
       </c>
       <c r="S21" s="36">
         <f t="shared" si="22"/>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="O22" s="20">
         <f t="shared" si="2"/>
-        <v>1.71966386825428</v>
+        <v>1.7330546027028808</v>
       </c>
       <c r="P22" s="5">
         <f t="shared" si="3"/>
@@ -4059,11 +4059,11 @@
       </c>
       <c r="Q22" s="7">
         <f t="shared" si="4"/>
-        <v>19.659917229472402</v>
+        <v>19.734323032812998</v>
       </c>
       <c r="R22" s="7">
         <f t="shared" si="5"/>
-        <v>39.539019801093083</v>
+        <v>39.381999910758097</v>
       </c>
       <c r="S22" s="36">
         <f t="shared" si="22"/>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="O23" s="20">
         <f t="shared" si="2"/>
-        <v>1.6195596260440268</v>
+        <v>1.6321708655288958</v>
       </c>
       <c r="P23" s="5">
         <f t="shared" si="3"/>
@@ -4213,11 +4213,11 @@
       </c>
       <c r="Q23" s="7">
         <f t="shared" si="4"/>
-        <v>20.412786269232726</v>
+        <v>20.490041414463207</v>
       </c>
       <c r="R23" s="7">
         <f t="shared" si="5"/>
-        <v>43.590628079921146</v>
+        <v>43.417518183035106</v>
       </c>
       <c r="S23" s="36">
         <f t="shared" si="22"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="O24" s="20">
         <f t="shared" si="2"/>
-        <v>1.6425114113285391</v>
+        <v>1.6553013725203298</v>
       </c>
       <c r="P24" s="5">
         <f t="shared" si="3"/>
@@ -4367,11 +4367,11 @@
       </c>
       <c r="Q24" s="7">
         <f t="shared" si="4"/>
-        <v>22.278398415680698</v>
+        <v>22.362714240203886</v>
       </c>
       <c r="R24" s="7">
         <f t="shared" si="5"/>
-        <v>46.909775109757184</v>
+        <v>46.723484003391185</v>
       </c>
       <c r="S24" s="36">
         <f t="shared" si="22"/>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="O25" s="20">
         <f t="shared" si="2"/>
-        <v>2.0016823797778596</v>
+        <v>2.0172691451294269</v>
       </c>
       <c r="P25" s="5">
         <f t="shared" si="3"/>
@@ -4521,11 +4521,11 @@
       </c>
       <c r="Q25" s="7">
         <f t="shared" si="4"/>
-        <v>28.691235464378209</v>
+        <v>28.799821599235429</v>
       </c>
       <c r="R25" s="7">
         <f t="shared" si="5"/>
-        <v>49.572618940955103</v>
+        <v>49.37575297844807</v>
       </c>
       <c r="S25" s="36">
         <f t="shared" si="22"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="O26" s="20">
         <f t="shared" si="2"/>
-        <v>2.0564095690405568</v>
+        <v>2.0724224858465239</v>
       </c>
       <c r="P26" s="5">
         <f t="shared" si="3"/>
@@ -4675,11 +4675,11 @@
       </c>
       <c r="Q26" s="7">
         <f t="shared" si="4"/>
-        <v>31.251040979028083</v>
+        <v>31.369315068493151</v>
       </c>
       <c r="R26" s="7">
         <f t="shared" si="5"/>
-        <v>52.558462503359905</v>
+        <v>52.349738967471318</v>
       </c>
       <c r="S26" s="36">
         <f t="shared" si="22"/>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="O27" s="20">
         <f t="shared" si="2"/>
-        <v>1.9254130802200009</v>
+        <v>1.9404059493132277</v>
       </c>
       <c r="P27" s="5">
         <f t="shared" si="3"/>
@@ -4829,11 +4829,11 @@
       </c>
       <c r="Q27" s="7">
         <f t="shared" si="4"/>
-        <v>31.070723099578533</v>
+        <v>31.188314749920359</v>
       </c>
       <c r="R27" s="7">
         <f t="shared" si="5"/>
-        <v>55.810411253471912</v>
+        <v>55.588773370219975</v>
       </c>
       <c r="S27" s="36">
         <f t="shared" si="22"/>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="O28" s="20">
         <f t="shared" si="2"/>
-        <v>2.0215846823560488</v>
+        <v>2.0373264236035808</v>
       </c>
       <c r="P28" s="5">
         <f t="shared" si="3"/>
@@ -4983,11 +4983,11 @@
       </c>
       <c r="Q28" s="7">
         <f t="shared" si="4"/>
-        <v>34.76311379678058</v>
+        <v>34.894679834342149</v>
       </c>
       <c r="R28" s="7">
         <f t="shared" si="5"/>
-        <v>59.472269509900535</v>
+        <v>59.236089420373908</v>
       </c>
       <c r="S28" s="36">
         <f t="shared" si="22"/>
@@ -5129,7 +5129,7 @@
       </c>
       <c r="O29" s="20">
         <f t="shared" si="2"/>
-        <v>2.4253225925543282</v>
+        <v>2.4442081732707828</v>
       </c>
       <c r="P29" s="5">
         <f t="shared" si="3"/>
@@ -5137,11 +5137,11 @@
       </c>
       <c r="Q29" s="7">
         <f t="shared" si="4"/>
-        <v>43.537322906616566</v>
+        <v>43.702096208983754</v>
       </c>
       <c r="R29" s="7">
         <f t="shared" si="5"/>
-        <v>62.084042648508188</v>
+        <v>61.837490518049158</v>
       </c>
       <c r="S29" s="36">
         <f t="shared" si="22"/>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="O30" s="20">
         <f t="shared" si="2"/>
-        <v>2.2044789096402626</v>
+        <v>2.2216448175955774</v>
       </c>
       <c r="P30" s="5">
         <f t="shared" si="3"/>
@@ -5291,11 +5291,11 @@
       </c>
       <c r="Q30" s="7">
         <f t="shared" si="4"/>
-        <v>41.218275529375923</v>
+        <v>41.374272061165975</v>
       </c>
       <c r="R30" s="7">
         <f t="shared" si="5"/>
-        <v>64.665352566974278</v>
+        <v>64.408549373075715</v>
       </c>
       <c r="S30" s="36">
         <f t="shared" si="22"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="O31" s="20">
         <f t="shared" si="2"/>
-        <v>2.5923568735243729</v>
+        <v>2.6125431222036624</v>
       </c>
       <c r="P31" s="5">
         <f t="shared" si="3"/>
@@ -5445,11 +5445,11 @@
       </c>
       <c r="Q31" s="7">
         <f t="shared" si="4"/>
-        <v>51.719443457065971</v>
+        <v>51.91518317935649</v>
       </c>
       <c r="R31" s="7">
         <f t="shared" si="5"/>
-        <v>68.999641609174802</v>
+        <v>68.725625808754614</v>
       </c>
       <c r="S31" s="36">
         <f t="shared" si="22"/>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O32" s="20">
         <f t="shared" si="2"/>
-        <v>2.4133789838258983</v>
+        <v>2.4321715616620851</v>
       </c>
       <c r="P32" s="5">
         <f t="shared" si="3"/>
@@ -5599,11 +5599,11 @@
       </c>
       <c r="Q32" s="7">
         <f t="shared" si="4"/>
-        <v>59.983852130198542</v>
+        <v>60.210869703727298</v>
       </c>
       <c r="R32" s="7">
         <f t="shared" si="5"/>
-        <v>85.960039422990747</v>
+        <v>85.61866940341794</v>
       </c>
       <c r="S32" s="36">
         <f t="shared" si="22"/>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="O33" s="20">
         <f t="shared" si="2"/>
-        <v>2.5755745649838429</v>
+        <v>2.5956301326380498</v>
       </c>
       <c r="P33" s="5">
         <f t="shared" si="3"/>
@@ -5753,11 +5753,11 @@
       </c>
       <c r="Q33" s="7">
         <f t="shared" si="4"/>
-        <v>72.042096176306302</v>
+        <v>72.314749920356803</v>
       </c>
       <c r="R33" s="7">
         <f t="shared" si="5"/>
-        <v>96.738643490726631</v>
+        <v>96.354468787648898</v>
       </c>
       <c r="S33" s="36">
         <f t="shared" si="22"/>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="O34" s="20">
         <f t="shared" si="2"/>
-        <v>2.1899329427253638</v>
+        <v>2.2069855836731831</v>
       </c>
       <c r="P34" s="5">
         <f t="shared" si="3"/>
@@ -5907,11 +5907,11 @@
       </c>
       <c r="Q34" s="7">
         <f t="shared" si="4"/>
-        <v>60.239679073782568</v>
+        <v>60.467664861420843</v>
       </c>
       <c r="R34" s="7">
         <f t="shared" si="5"/>
-        <v>95.134844547979569</v>
+        <v>94.757038954085033</v>
       </c>
       <c r="S34" s="36">
         <f t="shared" si="22"/>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="O35" s="20">
         <f t="shared" si="2"/>
-        <v>2.6626500813481426</v>
+        <v>2.683383691460608</v>
       </c>
       <c r="P35" s="5">
         <f t="shared" si="3"/>
@@ -6060,11 +6060,11 @@
       </c>
       <c r="Q35" s="7">
         <f t="shared" si="4"/>
-        <v>71.964657492510028</v>
+        <v>72.237018158649249</v>
       </c>
       <c r="R35" s="7">
         <f t="shared" si="5"/>
-        <v>93.472807096138325</v>
+        <v>93.101601891928041</v>
       </c>
       <c r="S35" s="36">
         <f t="shared" si="22"/>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="O36" s="20">
         <f t="shared" si="2"/>
-        <v>3.1730243786398979</v>
+        <v>3.1977321879029001</v>
       </c>
       <c r="P36" s="5">
         <f t="shared" si="3"/>
@@ -6214,11 +6214,11 @@
       </c>
       <c r="Q36" s="7">
         <f t="shared" si="4"/>
-        <v>88.149342405931051</v>
+        <v>88.48295635552725</v>
       </c>
       <c r="R36" s="7">
         <f t="shared" si="5"/>
-        <v>96.080100349431049</v>
+        <v>95.698540895096144</v>
       </c>
       <c r="S36" s="36">
         <f t="shared" si="22"/>
@@ -6312,41 +6312,41 @@
         <v>2025</v>
       </c>
       <c r="B37" s="19">
-        <v>3.5819999999999999</v>
+        <v>3.6080000000000001</v>
       </c>
       <c r="C37" s="20">
-        <v>4.1189999999999998</v>
+        <v>4.1890000000000001</v>
       </c>
       <c r="D37" s="20">
         <f>C37-B37</f>
-        <v>0.53699999999999992</v>
+        <v>0.58099999999999996</v>
       </c>
       <c r="E37" s="30">
-        <v>3.88</v>
+        <v>3.72</v>
       </c>
       <c r="F37" s="10">
         <f>Monitor!AE37</f>
-        <v>26257.333333333332</v>
+        <v>26158.333333333332</v>
       </c>
       <c r="G37" s="21">
         <f>(F37*100/F36)-100</f>
-        <v>13.443841179774452</v>
+        <v>13.016115327563099</v>
       </c>
       <c r="H37" s="20">
         <f>Monitor!Y37</f>
-        <v>22.321999999999999</v>
+        <v>22.411000000000001</v>
       </c>
       <c r="I37" s="38">
         <f>(H37*100/H36)-100</f>
-        <v>4.0798246841049917</v>
+        <v>4.4948011376882704</v>
       </c>
       <c r="J37" s="10">
         <f>AF37</f>
-        <v>167.08784376332088</v>
+        <v>165.79681176586712</v>
       </c>
       <c r="K37" s="5">
         <f ca="1">AVERAGE(OFFSET(J38,-14,0,14,1))</f>
-        <v>115.06185534546835</v>
+        <v>114.96963877422165</v>
       </c>
       <c r="L37" s="13">
         <v>2.65</v>
@@ -6356,11 +6356,11 @@
       </c>
       <c r="N37" s="13">
         <f t="shared" si="1"/>
-        <v>1.4298246841049917</v>
+        <v>1.8448011376882705</v>
       </c>
       <c r="O37" s="20">
         <f t="shared" si="2"/>
-        <v>3.4585000000000004</v>
+        <v>3.4584999999999999</v>
       </c>
       <c r="P37" s="5">
         <f t="shared" si="3"/>
@@ -6372,11 +6372,11 @@
       </c>
       <c r="R37" s="7">
         <f t="shared" si="5"/>
-        <v>100</v>
+        <v>99.999999999999986</v>
       </c>
       <c r="S37" s="36">
         <f t="shared" si="22"/>
-        <v>-1.0250000000000004</v>
+        <v>-1.1850000000000001</v>
       </c>
       <c r="T37" s="35">
         <f t="shared" si="6"/>
@@ -6390,75 +6390,229 @@
       </c>
       <c r="W37" s="3">
         <f t="shared" si="7"/>
-        <v>6.0612496152662354</v>
+        <v>6.0383964296706676</v>
       </c>
       <c r="X37" s="3">
         <f t="shared" si="8"/>
-        <v>3.4555205846176107</v>
+        <v>3.4896172491136679</v>
       </c>
       <c r="Y37" s="13">
-        <v>22.321999999999999</v>
+        <v>22.411000000000001</v>
       </c>
       <c r="Z37" s="13">
         <f>(Y37*100/Y36)-100</f>
-        <v>4.0798246841049917</v>
+        <v>4.4948011376882704</v>
       </c>
       <c r="AA37" s="13">
         <f>Y37-Y36</f>
-        <v>0.875</v>
+        <v>0.96400000000000219</v>
       </c>
       <c r="AB37" s="22">
-        <v>48445</v>
+        <v>48382</v>
       </c>
       <c r="AC37" s="22">
-        <v>6896</v>
+        <v>6858</v>
       </c>
       <c r="AD37" s="22">
-        <v>23431</v>
+        <v>23235</v>
       </c>
       <c r="AE37" s="10">
         <f>AVERAGE(AB37:AD37)</f>
-        <v>26257.333333333332</v>
+        <v>26158.333333333332</v>
       </c>
       <c r="AF37" s="13">
         <f>((AE37/Y37)/100)*100/7.04</f>
-        <v>167.08784376332088</v>
+        <v>165.79681176586712</v>
       </c>
       <c r="AG37" s="26">
         <f>AE37/Y37</f>
-        <v>1176.298420093779</v>
+        <v>1167.2095548317045</v>
       </c>
       <c r="AH37" s="13">
-        <v>17.085000000000001</v>
+        <v>17.23</v>
       </c>
       <c r="AI37" s="13">
         <f>(AH37*100/AH36)-100</f>
-        <v>2.4219171512499145</v>
+        <v>3.2911695941490251</v>
       </c>
       <c r="AJ37" s="20">
         <f>AH37-AH36</f>
-        <v>0.40399999999999991</v>
+        <v>0.54899999999999949</v>
       </c>
       <c r="AK37" s="22">
-        <v>8112</v>
+        <v>8195</v>
       </c>
       <c r="AL37" s="22">
-        <v>24344</v>
+        <v>24539</v>
       </c>
       <c r="AM37" s="22">
-        <v>5751</v>
+        <v>5850</v>
       </c>
       <c r="AN37" s="7">
         <f>AVERAGE(AK37:AM37)</f>
-        <v>12735.666666666666</v>
+        <v>12861.333333333334</v>
       </c>
       <c r="AO37" s="3">
         <f t="shared" si="9"/>
-        <v>116.34613924991835</v>
+        <v>116.50538322568271</v>
       </c>
       <c r="AP37" s="10">
         <f t="shared" si="18"/>
-        <v>745.42971417422689</v>
+        <v>746.44999032694909</v>
+      </c>
+    </row>
+    <row r="38" spans="1:42" s="31" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B38" s="19">
+        <v>3.605</v>
+      </c>
+      <c r="C38" s="20">
+        <v>4.141</v>
+      </c>
+      <c r="D38" s="20">
+        <f>C38-B38</f>
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="E38" s="30">
+        <v>3.64</v>
+      </c>
+      <c r="F38" s="10">
+        <f>Monitor!AE38</f>
+        <v>26837</v>
+      </c>
+      <c r="G38" s="21">
+        <f>(F38*100/F37)-100</f>
+        <v>2.5944568333864311</v>
+      </c>
+      <c r="H38" s="20">
+        <f>Monitor!Y38</f>
+        <v>22.411000000000001</v>
+      </c>
+      <c r="I38" s="38">
+        <f>(H38*100/H37)-100</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="10">
+        <f>AF38</f>
+        <v>170.09833847826349</v>
+      </c>
+      <c r="K38" s="5">
+        <f ca="1">AVERAGE(OFFSET(J39,-14,0,14,1))</f>
+        <v>121.45142099920645</v>
+      </c>
+      <c r="L38" s="13">
+        <v>2.65</v>
+      </c>
+      <c r="M38" s="10">
+        <v>96</v>
+      </c>
+      <c r="N38" s="13">
+        <f t="shared" ref="N38" si="25">I38-L38</f>
+        <v>-2.65</v>
+      </c>
+      <c r="O38" s="20">
+        <f t="shared" ref="O38" si="26">J38*MAX($D$2:$D$37)/MAX($J$2:$J$37)</f>
+        <v>3.5482292895826695</v>
+      </c>
+      <c r="P38" s="5">
+        <f t="shared" ref="P38" si="27">L38*MAX($D$2:$D$37)/MAX($L$2:$L$37)</f>
+        <v>1.145628125</v>
+      </c>
+      <c r="Q38" s="7">
+        <f t="shared" ref="Q38" si="28">(F38*100/MAX($F$2:$F$37))</f>
+        <v>102.59445683338643</v>
+      </c>
+      <c r="R38" s="7">
+        <f t="shared" ref="R38" si="29">(H38*MAX($Q$2:$Q$37)/MAX($H$2:$H$37))</f>
+        <v>99.999999999999986</v>
+      </c>
+      <c r="S38" s="36">
+        <f t="shared" ref="S38" si="30">E38-(AVERAGE(E36:E37))</f>
+        <v>-0.46000000000000041</v>
+      </c>
+      <c r="T38" s="35">
+        <f t="shared" ref="T38" si="31">IF(D38&gt;0,-0.5,1)+IF(J38&gt;100,1,-0.5)+IF(M38&gt;100,1,-0.5)+IF(S38&gt;1,1,-0.5)+IF(L38&gt;I38,1,-0.5)</f>
+        <v>0.5</v>
+      </c>
+      <c r="U38" s="10">
+        <v>5048</v>
+      </c>
+      <c r="V38" s="10">
+        <v>4243</v>
+      </c>
+      <c r="W38" s="3">
+        <f>F38/U38</f>
+        <v>5.316362916006339</v>
+      </c>
+      <c r="X38" s="3">
+        <f t="shared" ref="X38" si="32">AN38/V38</f>
+        <v>3.0935658732029223</v>
+      </c>
+      <c r="Y38" s="13">
+        <v>22.411000000000001</v>
+      </c>
+      <c r="Z38" s="13">
+        <f>(Y38*100/Y37)-100</f>
+        <v>0</v>
+      </c>
+      <c r="AA38" s="13">
+        <f>Y38-Y37</f>
+        <v>0</v>
+      </c>
+      <c r="AB38" s="22">
+        <v>50324</v>
+      </c>
+      <c r="AC38" s="22">
+        <v>6964</v>
+      </c>
+      <c r="AD38" s="22">
+        <v>23223</v>
+      </c>
+      <c r="AE38" s="10">
+        <f>AVERAGE(AB38:AD38)</f>
+        <v>26837</v>
+      </c>
+      <c r="AF38" s="13">
+        <f>((AE38/Y38)/100)*100/7.04</f>
+        <v>170.09833847826349</v>
+      </c>
+      <c r="AG38" s="26">
+        <f>AE38/Y38</f>
+        <v>1197.492302886975</v>
+      </c>
+      <c r="AH38" s="13">
+        <v>17.23</v>
+      </c>
+      <c r="AI38" s="13">
+        <f>(AH38*100/AH37)-100</f>
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="20">
+        <f>AH38-AH37</f>
+        <v>0</v>
+      </c>
+      <c r="AK38" s="22">
+        <v>8327</v>
+      </c>
+      <c r="AL38" s="22">
+        <v>25003</v>
+      </c>
+      <c r="AM38" s="22">
+        <v>6048</v>
+      </c>
+      <c r="AN38" s="7">
+        <f>AVERAGE(AK38:AM38)</f>
+        <v>13126</v>
+      </c>
+      <c r="AO38" s="3">
+        <f t="shared" ref="AO38" si="33">((AN38/AH38)/100)*100/6.407</f>
+        <v>118.90288670591265</v>
+      </c>
+      <c r="AP38" s="10">
+        <f t="shared" ref="AP38" si="34">AN38/AH38</f>
+        <v>761.81079512478232</v>
       </c>
     </row>
   </sheetData>
@@ -6466,7 +6620,7 @@
     <sortCondition descending="1" ref="C38:C42"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="D2:D37">
+  <conditionalFormatting sqref="D2:D38">
     <cfRule type="dataBar" priority="38">
       <dataBar>
         <cfvo type="min"/>
@@ -6480,7 +6634,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E37">
+  <conditionalFormatting sqref="E2:E38">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -6492,7 +6646,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G37">
+  <conditionalFormatting sqref="G2:G38">
     <cfRule type="dataBar" priority="39">
       <dataBar>
         <cfvo type="min"/>
@@ -6506,7 +6660,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I37">
+  <conditionalFormatting sqref="I2:I38">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -6518,7 +6672,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J37">
+  <conditionalFormatting sqref="J1:J38">
     <cfRule type="colorScale" priority="35">
       <colorScale>
         <cfvo type="min"/>
@@ -6530,7 +6684,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J37">
+  <conditionalFormatting sqref="J2:J38">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -6542,7 +6696,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L37">
+  <conditionalFormatting sqref="L2:L38">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -6554,7 +6708,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M37">
+  <conditionalFormatting sqref="M2:M38">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -6566,13 +6720,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S37">
+  <conditionalFormatting sqref="S2:S38">
     <cfRule type="cellIs" dxfId="1" priority="23" operator="between">
       <formula>1</formula>
       <formula>20</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T37">
+  <conditionalFormatting sqref="T2:T38">
     <cfRule type="cellIs" dxfId="0" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -6595,7 +6749,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D2:D37</xm:sqref>
+          <xm:sqref>D2:D38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{1E3255F2-7C0D-4421-87E8-7CC5D5E6C9BF}">
@@ -6606,7 +6760,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>G2:G37</xm:sqref>
+          <xm:sqref>G2:G38</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/public/market_data.xlsx
+++ b/public/market_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ismae\Documents\GitHub\galetaireID\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7844D2-5B41-4481-9762-CD2E0B90F597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52AD142B-8F9F-4773-8E09-1F74C7555518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{CD70AFFB-D9AB-4B42-B823-CE9D5850E5EA}"/>
   </bookViews>
@@ -5703,7 +5703,7 @@
         <v>1.5740000000000001</v>
       </c>
       <c r="D33" s="20">
-        <f>C33-B33</f>
+        <f t="shared" ref="D33:D38" si="24">C33-B33</f>
         <v>1.3740000000000001</v>
       </c>
       <c r="E33" s="23">
@@ -5722,7 +5722,7 @@
         <v>21.594000000000001</v>
       </c>
       <c r="I33" s="38">
-        <f>(H33*100/H32)-100</f>
+        <f t="shared" ref="I33:I38" si="25">(H33*100/H32)-100</f>
         <v>12.53908692933085</v>
       </c>
       <c r="J33" s="7">
@@ -5857,7 +5857,7 @@
         <v>3.87</v>
       </c>
       <c r="D34" s="20">
-        <f>C34-B34</f>
+        <f t="shared" si="24"/>
         <v>-0.88999999999999968</v>
       </c>
       <c r="E34" s="24">
@@ -5876,7 +5876,7 @@
         <v>21.236000000000001</v>
       </c>
       <c r="I34" s="38">
-        <f>(H34*100/H33)-100</f>
+        <f t="shared" si="25"/>
         <v>-1.6578679262758271</v>
       </c>
       <c r="J34" s="7">
@@ -6011,7 +6011,7 @@
         <v>3.86</v>
       </c>
       <c r="D35" s="20">
-        <f>C35-B35</f>
+        <f t="shared" si="24"/>
         <v>-1.4</v>
       </c>
       <c r="E35" s="24">
@@ -6029,7 +6029,7 @@
         <v>20.864999999999998</v>
       </c>
       <c r="I35" s="38">
-        <f>(H35*100/H34)-100</f>
+        <f t="shared" si="25"/>
         <v>-1.7470333396119884</v>
       </c>
       <c r="J35" s="7">
@@ -6164,7 +6164,7 @@
         <v>4.57</v>
       </c>
       <c r="D36" s="20">
-        <f>C36-B36</f>
+        <f t="shared" si="24"/>
         <v>0.3100000000000005</v>
       </c>
       <c r="E36" s="39">
@@ -6175,7 +6175,7 @@
         <v>23145.666666666668</v>
       </c>
       <c r="G36" s="21">
-        <f t="shared" ref="G36" si="24">(F36*100/F35)-100</f>
+        <f t="shared" ref="G36" si="26">(F36*100/F35)-100</f>
         <v>22.489768557719458</v>
       </c>
       <c r="H36" s="20">
@@ -6183,7 +6183,7 @@
         <v>21.446999999999999</v>
       </c>
       <c r="I36" s="38">
-        <f>(H36*100/H35)-100</f>
+        <f t="shared" si="25"/>
         <v>2.7893601725377408</v>
       </c>
       <c r="J36" s="10">
@@ -6318,7 +6318,7 @@
         <v>4.1890000000000001</v>
       </c>
       <c r="D37" s="20">
-        <f>C37-B37</f>
+        <f t="shared" si="24"/>
         <v>0.58099999999999996</v>
       </c>
       <c r="E37" s="30">
@@ -6337,7 +6337,7 @@
         <v>22.411000000000001</v>
       </c>
       <c r="I37" s="38">
-        <f>(H37*100/H36)-100</f>
+        <f t="shared" si="25"/>
         <v>4.4948011376882704</v>
       </c>
       <c r="J37" s="10">
@@ -6349,14 +6349,14 @@
         <v>114.96963877422165</v>
       </c>
       <c r="L37" s="13">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="M37" s="10">
         <v>98</v>
       </c>
       <c r="N37" s="13">
         <f t="shared" si="1"/>
-        <v>1.8448011376882705</v>
+        <v>1.8948011376882703</v>
       </c>
       <c r="O37" s="20">
         <f t="shared" si="2"/>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P37" s="5">
         <f t="shared" si="3"/>
-        <v>1.145628125</v>
+        <v>1.1240125000000001</v>
       </c>
       <c r="Q37" s="7">
         <f t="shared" si="4"/>
@@ -6472,7 +6472,7 @@
         <v>4.141</v>
       </c>
       <c r="D38" s="20">
-        <f>C38-B38</f>
+        <f t="shared" si="24"/>
         <v>0.53600000000000003</v>
       </c>
       <c r="E38" s="30">
@@ -6491,7 +6491,7 @@
         <v>22.411000000000001</v>
       </c>
       <c r="I38" s="38">
-        <f>(H38*100/H37)-100</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="J38" s="10">
@@ -6509,31 +6509,31 @@
         <v>96</v>
       </c>
       <c r="N38" s="13">
-        <f t="shared" ref="N38" si="25">I38-L38</f>
+        <f t="shared" ref="N38" si="27">I38-L38</f>
         <v>-2.65</v>
       </c>
       <c r="O38" s="20">
-        <f t="shared" ref="O38" si="26">J38*MAX($D$2:$D$37)/MAX($J$2:$J$37)</f>
+        <f t="shared" ref="O38" si="28">J38*MAX($D$2:$D$37)/MAX($J$2:$J$37)</f>
         <v>3.5482292895826695</v>
       </c>
       <c r="P38" s="5">
-        <f t="shared" ref="P38" si="27">L38*MAX($D$2:$D$37)/MAX($L$2:$L$37)</f>
+        <f t="shared" ref="P38" si="29">L38*MAX($D$2:$D$37)/MAX($L$2:$L$37)</f>
         <v>1.145628125</v>
       </c>
       <c r="Q38" s="7">
-        <f t="shared" ref="Q38" si="28">(F38*100/MAX($F$2:$F$37))</f>
+        <f t="shared" ref="Q38" si="30">(F38*100/MAX($F$2:$F$37))</f>
         <v>102.59445683338643</v>
       </c>
       <c r="R38" s="7">
-        <f t="shared" ref="R38" si="29">(H38*MAX($Q$2:$Q$37)/MAX($H$2:$H$37))</f>
+        <f t="shared" ref="R38" si="31">(H38*MAX($Q$2:$Q$37)/MAX($H$2:$H$37))</f>
         <v>99.999999999999986</v>
       </c>
       <c r="S38" s="36">
-        <f t="shared" ref="S38" si="30">E38-(AVERAGE(E36:E37))</f>
+        <f t="shared" ref="S38" si="32">E38-(AVERAGE(E36:E37))</f>
         <v>-0.46000000000000041</v>
       </c>
       <c r="T38" s="35">
-        <f t="shared" ref="T38" si="31">IF(D38&gt;0,-0.5,1)+IF(J38&gt;100,1,-0.5)+IF(M38&gt;100,1,-0.5)+IF(S38&gt;1,1,-0.5)+IF(L38&gt;I38,1,-0.5)</f>
+        <f t="shared" ref="T38" si="33">IF(D38&gt;0,-0.5,1)+IF(J38&gt;100,1,-0.5)+IF(M38&gt;100,1,-0.5)+IF(S38&gt;1,1,-0.5)+IF(L38&gt;I38,1,-0.5)</f>
         <v>0.5</v>
       </c>
       <c r="U38" s="10">
@@ -6547,7 +6547,7 @@
         <v>5.316362916006339</v>
       </c>
       <c r="X38" s="3">
-        <f t="shared" ref="X38" si="32">AN38/V38</f>
+        <f t="shared" ref="X38" si="34">AN38/V38</f>
         <v>3.0935658732029223</v>
       </c>
       <c r="Y38" s="13">
@@ -6607,11 +6607,11 @@
         <v>13126</v>
       </c>
       <c r="AO38" s="3">
-        <f t="shared" ref="AO38" si="33">((AN38/AH38)/100)*100/6.407</f>
+        <f t="shared" ref="AO38" si="35">((AN38/AH38)/100)*100/6.407</f>
         <v>118.90288670591265</v>
       </c>
       <c r="AP38" s="10">
-        <f t="shared" ref="AP38" si="34">AN38/AH38</f>
+        <f t="shared" ref="AP38" si="36">AN38/AH38</f>
         <v>761.81079512478232</v>
       </c>
     </row>

--- a/public/market_data.xlsx
+++ b/public/market_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ismae\Documents\GitHub\galetaireID\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52AD142B-8F9F-4773-8E09-1F74C7555518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92386DE4-F276-45E3-A8B3-354E96A58EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{CD70AFFB-D9AB-4B42-B823-CE9D5850E5EA}"/>
   </bookViews>
@@ -6466,55 +6466,55 @@
         <v>2026</v>
       </c>
       <c r="B38" s="19">
-        <v>3.605</v>
+        <v>3.706</v>
       </c>
       <c r="C38" s="20">
-        <v>4.141</v>
+        <v>4.3780000000000001</v>
       </c>
       <c r="D38" s="20">
         <f t="shared" si="24"/>
-        <v>0.53600000000000003</v>
+        <v>0.67200000000000015</v>
       </c>
       <c r="E38" s="30">
         <v>3.64</v>
       </c>
       <c r="F38" s="10">
         <f>Monitor!AE38</f>
-        <v>26837</v>
+        <v>27281</v>
       </c>
       <c r="G38" s="21">
         <f>(F38*100/F37)-100</f>
-        <v>2.5944568333864311</v>
+        <v>4.2918126791972071</v>
       </c>
       <c r="H38" s="20">
         <f>Monitor!Y38</f>
-        <v>22.411000000000001</v>
+        <v>22.686</v>
       </c>
       <c r="I38" s="38">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>1.2270759894694407</v>
       </c>
       <c r="J38" s="10">
         <f>AF38</f>
-        <v>170.09833847826349</v>
+        <v>170.81645267806334</v>
       </c>
       <c r="K38" s="5">
         <f ca="1">AVERAGE(OFFSET(J39,-14,0,14,1))</f>
-        <v>121.45142099920645</v>
+        <v>121.50271487062072</v>
       </c>
       <c r="L38" s="13">
         <v>2.65</v>
       </c>
       <c r="M38" s="10">
-        <v>96</v>
+        <v>98.16</v>
       </c>
       <c r="N38" s="13">
         <f t="shared" ref="N38" si="27">I38-L38</f>
-        <v>-2.65</v>
+        <v>-1.4229240105305592</v>
       </c>
       <c r="O38" s="20">
         <f t="shared" ref="O38" si="28">J38*MAX($D$2:$D$37)/MAX($J$2:$J$37)</f>
-        <v>3.5482292895826695</v>
+        <v>3.5632090586961738</v>
       </c>
       <c r="P38" s="5">
         <f t="shared" ref="P38" si="29">L38*MAX($D$2:$D$37)/MAX($L$2:$L$37)</f>
@@ -6522,11 +6522,11 @@
       </c>
       <c r="Q38" s="7">
         <f t="shared" ref="Q38" si="30">(F38*100/MAX($F$2:$F$37))</f>
-        <v>102.59445683338643</v>
+        <v>104.29181267919721</v>
       </c>
       <c r="R38" s="7">
         <f t="shared" ref="R38" si="31">(H38*MAX($Q$2:$Q$37)/MAX($H$2:$H$37))</f>
-        <v>99.999999999999986</v>
+        <v>101.22707598946943</v>
       </c>
       <c r="S38" s="36">
         <f t="shared" ref="S38" si="32">E38-(AVERAGE(E36:E37))</f>
@@ -6537,82 +6537,82 @@
         <v>0.5</v>
       </c>
       <c r="U38" s="10">
-        <v>5048</v>
+        <v>4661</v>
       </c>
       <c r="V38" s="10">
-        <v>4243</v>
+        <v>3936</v>
       </c>
       <c r="W38" s="3">
         <f>F38/U38</f>
-        <v>5.316362916006339</v>
+        <v>5.8530358292211968</v>
       </c>
       <c r="X38" s="3">
-        <f t="shared" ref="X38" si="34">AN38/V38</f>
-        <v>3.0935658732029223</v>
+        <f>AN38/V38</f>
+        <v>3.2424627371273713</v>
       </c>
       <c r="Y38" s="13">
-        <v>22.411000000000001</v>
+        <v>22.686</v>
       </c>
       <c r="Z38" s="13">
         <f>(Y38*100/Y37)-100</f>
-        <v>0</v>
+        <v>1.2270759894694407</v>
       </c>
       <c r="AA38" s="13">
         <f>Y38-Y37</f>
-        <v>0</v>
+        <v>0.27499999999999858</v>
       </c>
       <c r="AB38" s="22">
-        <v>50324</v>
+        <v>49499</v>
       </c>
       <c r="AC38" s="22">
-        <v>6964</v>
+        <v>7230</v>
       </c>
       <c r="AD38" s="22">
-        <v>23223</v>
+        <v>25114</v>
       </c>
       <c r="AE38" s="10">
         <f>AVERAGE(AB38:AD38)</f>
-        <v>26837</v>
+        <v>27281</v>
       </c>
       <c r="AF38" s="13">
         <f>((AE38/Y38)/100)*100/7.04</f>
-        <v>170.09833847826349</v>
+        <v>170.81645267806334</v>
       </c>
       <c r="AG38" s="26">
         <f>AE38/Y38</f>
-        <v>1197.492302886975</v>
+        <v>1202.547826853566</v>
       </c>
       <c r="AH38" s="13">
-        <v>17.23</v>
+        <v>17.446000000000002</v>
       </c>
       <c r="AI38" s="13">
         <f>(AH38*100/AH37)-100</f>
-        <v>0</v>
+        <v>1.2536273940800982</v>
       </c>
       <c r="AJ38" s="20">
         <f>AH38-AH37</f>
-        <v>0</v>
+        <v>0.21600000000000108</v>
       </c>
       <c r="AK38" s="22">
-        <v>8327</v>
+        <v>8114</v>
       </c>
       <c r="AL38" s="22">
-        <v>25003</v>
+        <v>24292</v>
       </c>
       <c r="AM38" s="22">
-        <v>6048</v>
+        <v>5881</v>
       </c>
       <c r="AN38" s="7">
         <f>AVERAGE(AK38:AM38)</f>
-        <v>13126</v>
+        <v>12762.333333333334</v>
       </c>
       <c r="AO38" s="3">
-        <f t="shared" ref="AO38" si="35">((AN38/AH38)/100)*100/6.407</f>
-        <v>118.90288670591265</v>
+        <f t="shared" ref="AO38" si="34">((AN38/AH38)/100)*100/6.407</f>
+        <v>114.17722706860867</v>
       </c>
       <c r="AP38" s="10">
-        <f t="shared" ref="AP38" si="36">AN38/AH38</f>
-        <v>761.81079512478232</v>
+        <f t="shared" ref="AP38" si="35">AN38/AH38</f>
+        <v>731.53349382857573</v>
       </c>
     </row>
   </sheetData>

--- a/public/market_data.xlsx
+++ b/public/market_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ismae\Documents\GitHub\galetaireID\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92386DE4-F276-45E3-A8B3-354E96A58EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F25342-BC97-4FAB-B814-F7BCE1203178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{CD70AFFB-D9AB-4B42-B823-CE9D5850E5EA}"/>
   </bookViews>
@@ -6466,153 +6466,153 @@
         <v>2026</v>
       </c>
       <c r="B38" s="19">
-        <v>3.706</v>
+        <v>3.9209999999999998</v>
       </c>
       <c r="C38" s="20">
-        <v>4.3780000000000001</v>
+        <v>4.6580000000000004</v>
       </c>
       <c r="D38" s="20">
         <f t="shared" si="24"/>
-        <v>0.67200000000000015</v>
+        <v>0.73700000000000054</v>
       </c>
       <c r="E38" s="30">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="F38" s="10">
         <f>Monitor!AE38</f>
-        <v>27281</v>
+        <v>29494.333333333332</v>
       </c>
       <c r="G38" s="21">
         <f>(F38*100/F37)-100</f>
-        <v>4.2918126791972071</v>
+        <v>12.753106084740352</v>
       </c>
       <c r="H38" s="20">
         <f>Monitor!Y38</f>
-        <v>22.686</v>
+        <v>23.155000000000001</v>
       </c>
       <c r="I38" s="38">
         <f t="shared" si="25"/>
-        <v>1.2270759894694407</v>
+        <v>3.3197983133282634</v>
       </c>
       <c r="J38" s="10">
         <f>AF38</f>
-        <v>170.81645267806334</v>
+        <v>180.93439796365729</v>
       </c>
       <c r="K38" s="5">
         <f ca="1">AVERAGE(OFFSET(J39,-14,0,14,1))</f>
-        <v>121.50271487062072</v>
+        <v>122.22542524816315</v>
       </c>
       <c r="L38" s="13">
-        <v>2.65</v>
+        <v>3.27</v>
       </c>
       <c r="M38" s="10">
-        <v>98.16</v>
+        <v>99.54</v>
       </c>
       <c r="N38" s="13">
         <f t="shared" ref="N38" si="27">I38-L38</f>
-        <v>-1.4229240105305592</v>
+        <v>4.9798313328263344E-2</v>
       </c>
       <c r="O38" s="20">
         <f t="shared" ref="O38" si="28">J38*MAX($D$2:$D$37)/MAX($J$2:$J$37)</f>
-        <v>3.5632090586961738</v>
+        <v>3.7742680856914728</v>
       </c>
       <c r="P38" s="5">
         <f t="shared" ref="P38" si="29">L38*MAX($D$2:$D$37)/MAX($L$2:$L$37)</f>
-        <v>1.145628125</v>
+        <v>1.4136618750000001</v>
       </c>
       <c r="Q38" s="7">
         <f t="shared" ref="Q38" si="30">(F38*100/MAX($F$2:$F$37))</f>
-        <v>104.29181267919721</v>
+        <v>112.75310608474035</v>
       </c>
       <c r="R38" s="7">
         <f t="shared" ref="R38" si="31">(H38*MAX($Q$2:$Q$37)/MAX($H$2:$H$37))</f>
-        <v>101.22707598946943</v>
+        <v>103.31979831332826</v>
       </c>
       <c r="S38" s="36">
         <f t="shared" ref="S38" si="32">E38-(AVERAGE(E36:E37))</f>
-        <v>-0.46000000000000041</v>
+        <v>-0.47000000000000064</v>
       </c>
       <c r="T38" s="35">
         <f t="shared" ref="T38" si="33">IF(D38&gt;0,-0.5,1)+IF(J38&gt;100,1,-0.5)+IF(M38&gt;100,1,-0.5)+IF(S38&gt;1,1,-0.5)+IF(L38&gt;I38,1,-0.5)</f>
-        <v>0.5</v>
+        <v>-1</v>
       </c>
       <c r="U38" s="10">
-        <v>4661</v>
+        <v>4401</v>
       </c>
       <c r="V38" s="10">
-        <v>3936</v>
+        <v>3757</v>
       </c>
       <c r="W38" s="3">
         <f>F38/U38</f>
-        <v>5.8530358292211968</v>
+        <v>6.7017344542906914</v>
       </c>
       <c r="X38" s="3">
         <f>AN38/V38</f>
-        <v>3.2424627371273713</v>
+        <v>3.6872504657971787</v>
       </c>
       <c r="Y38" s="13">
-        <v>22.686</v>
+        <v>23.155000000000001</v>
       </c>
       <c r="Z38" s="13">
         <f>(Y38*100/Y37)-100</f>
-        <v>1.2270759894694407</v>
+        <v>3.3197983133282634</v>
       </c>
       <c r="AA38" s="13">
         <f>Y38-Y37</f>
-        <v>0.27499999999999858</v>
+        <v>0.74399999999999977</v>
       </c>
       <c r="AB38" s="22">
-        <v>49499</v>
+        <v>54036</v>
       </c>
       <c r="AC38" s="22">
-        <v>7230</v>
+        <v>7757</v>
       </c>
       <c r="AD38" s="22">
-        <v>25114</v>
+        <v>26690</v>
       </c>
       <c r="AE38" s="10">
         <f>AVERAGE(AB38:AD38)</f>
-        <v>27281</v>
+        <v>29494.333333333332</v>
       </c>
       <c r="AF38" s="13">
         <f>((AE38/Y38)/100)*100/7.04</f>
-        <v>170.81645267806334</v>
+        <v>180.93439796365729</v>
       </c>
       <c r="AG38" s="26">
         <f>AE38/Y38</f>
-        <v>1202.547826853566</v>
+        <v>1273.7781616641473</v>
       </c>
       <c r="AH38" s="13">
-        <v>17.446000000000002</v>
+        <v>17.61</v>
       </c>
       <c r="AI38" s="13">
         <f>(AH38*100/AH37)-100</f>
-        <v>1.2536273940800982</v>
+        <v>2.2054556006964532</v>
       </c>
       <c r="AJ38" s="20">
         <f>AH38-AH37</f>
-        <v>0.21600000000000108</v>
+        <v>0.37999999999999901</v>
       </c>
       <c r="AK38" s="22">
-        <v>8114</v>
+        <v>8714</v>
       </c>
       <c r="AL38" s="22">
-        <v>24292</v>
+        <v>26319</v>
       </c>
       <c r="AM38" s="22">
-        <v>5881</v>
+        <v>6526</v>
       </c>
       <c r="AN38" s="7">
         <f>AVERAGE(AK38:AM38)</f>
-        <v>12762.333333333334</v>
+        <v>13853</v>
       </c>
       <c r="AO38" s="3">
         <f t="shared" ref="AO38" si="34">((AN38/AH38)/100)*100/6.407</f>
-        <v>114.17722706860867</v>
+        <v>122.78060082460561</v>
       </c>
       <c r="AP38" s="10">
         <f t="shared" ref="AP38" si="35">AN38/AH38</f>
-        <v>731.53349382857573</v>
+        <v>786.65530948324817</v>
       </c>
     </row>
   </sheetData>
